--- a/data/ai_content_os.xlsx
+++ b/data/ai_content_os.xlsx
@@ -1288,7 +1288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1320,21 +1320,21 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>alice</t>
+          <t>debug_user</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>alice@example.com</t>
+          <t>debug@example.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-22T10:00:00</t>
+          <t>2026-06-22T12:00:00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1345,26 +1345,51 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>1019994796</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>bob</t>
+          <t>gost3n</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bob@example.com</t>
+          <t>test@gmail.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-06-22T11:00:00</t>
+          <t>2026-06-22T07:59:50.337115+00:00</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>bot_test</t>
+          <t>bot_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5815131170</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>a91683</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>test@yandex.ru</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-06-22T08:00:49.302248+00:00</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>bot_v1</t>
         </is>
       </c>
     </row>
@@ -2066,9 +2091,9 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A11:F11"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A16:F16"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A3:F3"/>
@@ -6231,6 +6256,7 @@
           <t>100 000 000 просмотров / месяц</t>
         </is>
       </c>
+      <c r="D6" s="136" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="8" t="inlineStr"/>
@@ -6244,6 +6270,7 @@
           <t>100 видео / день · 3 000 / месяц</t>
         </is>
       </c>
+      <c r="D7" s="136" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="5" t="inlineStr"/>
@@ -6257,6 +6284,7 @@
           <t>15 нишевых Instagram-аккаунтов</t>
         </is>
       </c>
+      <c r="D8" s="136" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="8" t="inlineStr"/>
@@ -6270,6 +6298,7 @@
           <t>Каждый сценарий = 1 из 6 психологических триггеров</t>
         </is>
       </c>
+      <c r="D9" s="136" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -6442,9 +6471,9 @@
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A5:D5"/>
     <mergeCell ref="B8"/>
     <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A5:D5"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="B9"/>
@@ -6831,6 +6860,7 @@
           <t>AI-пайплайн производит объём, человек контролирует только QC-шлюз перед публикацией (см. 05 Pipeline).</t>
         </is>
       </c>
+      <c r="C30" s="136" t="n"/>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="34" t="inlineStr">
@@ -6843,6 +6873,7 @@
           <t>15 аккаунтов = 15 чётких тем. Критично для алгоритмических topic-controls Instagram (см. 10 Reality Check).</t>
         </is>
       </c>
+      <c r="C31" s="136" t="n"/>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="31" t="inlineStr">
@@ -6855,6 +6886,7 @@
           <t>Еженедельно: нижние 20% по retention — в архив, верхние 20% — удваиваем формат (см. 08 KPI Dashboard).</t>
         </is>
       </c>
+      <c r="C32" s="136" t="n"/>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="34" t="inlineStr">
@@ -6867,6 +6899,7 @@
           <t>Сценарий не пишется, пока хук не закреплён за одним из 6 принципов (см. 03 Psychology, 04 Content Engine).</t>
         </is>
       </c>
+      <c r="C33" s="136" t="n"/>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="31" t="inlineStr">
@@ -6879,6 +6912,7 @@
           <t>Холодный охват через психологию → тёплая аудитория через идентичность/регулярность → конверсия в промо-слоте.</t>
         </is>
       </c>
+      <c r="C34" s="136" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -7848,6 +7882,7 @@
           <t>Когда использовать в первую очередь</t>
         </is>
       </c>
+      <c r="E15" s="136" t="n"/>
     </row>
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="55" t="inlineStr">
@@ -7870,6 +7905,7 @@
           <t>Постоянные рубрики, серийный контент, фирменные открывашки аккаунта.</t>
         </is>
       </c>
+      <c r="E16" s="136" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="58" t="inlineStr">
@@ -7892,6 +7928,7 @@
           <t>Хук видео, особенно для туториалов и сравнений.</t>
         </is>
       </c>
+      <c r="E17" s="136" t="n"/>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="55" t="inlineStr">
@@ -7914,6 +7951,7 @@
           <t>Контент для тёплой/горячей аудитории, нативный промо-слот.</t>
         </is>
       </c>
+      <c r="E18" s="136" t="n"/>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="58" t="inlineStr">
@@ -7936,6 +7974,7 @@
           <t>Первый кадр любого видео — независимо от пилларa.</t>
         </is>
       </c>
+      <c r="E19" s="136" t="n"/>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="55" t="inlineStr">
@@ -7958,6 +7997,7 @@
           <t>Listicle/сравнения и payoff-моменты, рассчитанные на пересылку.</t>
         </is>
       </c>
+      <c r="E20" s="136" t="n"/>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="58" t="inlineStr">
@@ -7980,6 +8020,7 @@
           <t>Базовый каркас сценария — применяется почти всегда поверх остальных.</t>
         </is>
       </c>
+      <c r="E21" s="136" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -10058,6 +10099,8 @@
           <t>Команда (см. 06 Team)</t>
         </is>
       </c>
+      <c r="B25" s="137" t="n"/>
+      <c r="C25" s="136" t="n"/>
       <c r="D25" s="98">
         <f>'👥 06 Team'!F14</f>
         <v/>
@@ -10070,6 +10113,8 @@
           <t>AI-инструменты (выше)</t>
         </is>
       </c>
+      <c r="B26" s="137" t="n"/>
+      <c r="C26" s="136" t="n"/>
       <c r="D26" s="99">
         <f>'🛠️ 07 AI Stack'!D22</f>
         <v/>
